--- a/data/trans_camb/IP1010-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1010-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,67</t>
+          <t>-0,44; 3,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,0</t>
+          <t>-2,3; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,95</t>
+          <t>-1,71; 0,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,66</t>
+          <t>-0,73; 3,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,46</t>
+          <t>-0,87; 1,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,8</t>
+          <t>-0,59; 1,86</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,0</t>
+          <t>-1,64; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,0</t>
+          <t>-1,89; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,0</t>
+          <t>-1,57; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,45</t>
+          <t>-0,66; 1,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,0</t>
+          <t>-1,14; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,61</t>
+          <t>-0,65; 0,61</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,6; -0,42</t>
+          <t>-3,54; -0,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,65; -0,43</t>
+          <t>-3,24; -0,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,05</t>
+          <t>-1,7; 0,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,1</t>
+          <t>-1,63; 0,04</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,94</t>
+          <t>-0,39; 1,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,59</t>
+          <t>-0,68; 1,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,96</t>
+          <t>-0,33; 1,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,61</t>
+          <t>-0,34; 0,78</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,62</t>
+          <t>-0,27; 0,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,11</t>
+          <t>-0,48; 0,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,25</t>
+          <t>-0,93; 0,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,71</t>
+          <t>-0,69; 0,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,24</t>
+          <t>-0,41; 0,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,32</t>
+          <t>-0,45; 0,35</t>
         </is>
       </c>
     </row>
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-89,99; 102,59</t>
+          <t>-89,54; 118,28</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-74,72; 261,99</t>
+          <t>-71,73; 224,48</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-78,87; 111,48</t>
+          <t>-72,93; 118,73</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-69,87; 167,94</t>
+          <t>-72,31; 149,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1010-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1010-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,66</t>
+          <t>-0,44; 3,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,0</t>
+          <t>-2,2; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,91</t>
+          <t>-1,91; 0,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,9</t>
+          <t>-0,83; 3,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,43</t>
+          <t>-0,85; 1,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,86</t>
+          <t>-0,67; 1,85</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,0</t>
+          <t>-1,89; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,0</t>
+          <t>-1,65; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,0</t>
+          <t>-1,27; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,47</t>
+          <t>-0,65; 1,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,0</t>
+          <t>-1,18; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,61</t>
+          <t>-0,66; 0,6</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; -0,43</t>
+          <t>-3,53; -0,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -0,43</t>
+          <t>-3,59; -0,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,03</t>
+          <t>-1,98; 0,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,04</t>
+          <t>-1,89; 0,01</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,94</t>
+          <t>-0,41; 1,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,26</t>
+          <t>-0,68; 1,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,07</t>
+          <t>-0,21; 1,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,78</t>
+          <t>-0,34; 0,66</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,62</t>
+          <t>-0,28; 0,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,13</t>
+          <t>-0,5; 0,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,26</t>
+          <t>-0,92; 0,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,71</t>
+          <t>-0,62; 0,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,26</t>
+          <t>-0,5; 0,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,35</t>
+          <t>-0,41; 0,32</t>
         </is>
       </c>
     </row>
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-89,54; 118,28</t>
+          <t>-88,19; 88,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-71,73; 224,48</t>
+          <t>-71,0; 220,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-72,93; 118,73</t>
+          <t>-79,6; 123,77</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-72,31; 149,18</t>
+          <t>-68,63; 145,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1010-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1010-Habitat-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,77</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-0,44</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,38</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,13</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,71</t>
+          <t>-1,84; 0,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,0</t>
+          <t>-0,75; 3,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,95</t>
+          <t>-0,75; 3,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,58</t>
+          <t>-2,25; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,5</t>
+          <t>-0,94; 1,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,85</t>
+          <t>-0,8; 1,8</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-46,12%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>135,45%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>177,61%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-46,12%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>135,45%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,31</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,28</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,33</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,33</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,0</t>
+          <t>-1,39; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,0</t>
+          <t>-0,65; 1,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>-1,56; 0,0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>-1,32; 0,0</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>-1,27; 0,0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,65; 1,23</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-1,18; 0,0</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,6</t>
+          <t>-0,64; 0,61</t>
         </is>
       </c>
     </row>
@@ -830,17 +830,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>89,09%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>89,09%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,35</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,35</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,34</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>-3,6; -0,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>-3,65; -0,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; -0,43</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -0,43</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,02</t>
+          <t>-1,78; 0,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,01</t>
+          <t>-1,7; 0,1</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,61</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,61</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,67; 1,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,68; 1,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,07</t>
+          <t>-0,19; 0,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,66</t>
+          <t>-0,34; 0,61</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>181,09%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>17,98%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>181,09%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>17,98%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,29</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,03</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,11</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,27 +1255,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,61</t>
+          <t>-0,93; 0,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,12</t>
+          <t>-0,64; 0,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,17</t>
+          <t>-0,26; 0,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,72</t>
+          <t>-0,46; 0,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,25</t>
+          <t>-0,52; 0,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-45,06%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>61,82%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-59,38%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-45,06%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,99; 102,59</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-74,72; 261,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-88,19; 88,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-71,0; 220,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-79,6; 123,77</t>
+          <t>-78,87; 111,48</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-68,63; 145,27</t>
+          <t>-69,87; 167,94</t>
         </is>
       </c>
     </row>
